--- a/reports/Orders_Report.xlsx
+++ b/reports/Orders_Report.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -459,16 +459,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Omkar</t>
+          <t>Sujal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-10-07 12:53:11.3800000</t>
+          <t>2026-10-09 15:35:47.3233333</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -477,29 +477,6 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Sujal Anvekar</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-10-07 10:50:58.7200000</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Completed</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
         <v>400</v>
       </c>
     </row>
